--- a/summary_stats/chuuchuu_summary_2025_09.xlsx
+++ b/summary_stats/chuuchuu_summary_2025_09.xlsx
@@ -1454,25 +1454,25 @@
         <v>62</v>
       </c>
       <c r="N13" t="n">
-        <v>1091</v>
+        <v>1066</v>
       </c>
       <c r="O13" t="n">
-        <v>914</v>
+        <v>892</v>
       </c>
       <c r="P13" t="n">
-        <v>844</v>
+        <v>822</v>
       </c>
       <c r="Q13" t="n">
-        <v>647</v>
+        <v>626</v>
       </c>
       <c r="R13" t="n">
-        <v>492</v>
+        <v>472</v>
       </c>
       <c r="S13" t="n">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="T13" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="U13" t="n">
         <v>1933</v>
@@ -1533,25 +1533,25 @@
         <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O14" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P14" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
         <v>54</v>
@@ -1612,25 +1612,25 @@
         <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="O15" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="P15" t="n">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="Q15" t="n">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="R15" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="S15" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="T15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="U15" t="n">
         <v>348</v>
@@ -1691,25 +1691,25 @@
         <v>740</v>
       </c>
       <c r="N16" t="n">
-        <v>2809</v>
+        <v>2487</v>
       </c>
       <c r="O16" t="n">
-        <v>2482</v>
+        <v>2172</v>
       </c>
       <c r="P16" t="n">
-        <v>2347</v>
+        <v>2043</v>
       </c>
       <c r="Q16" t="n">
-        <v>1890</v>
+        <v>1622</v>
       </c>
       <c r="R16" t="n">
-        <v>1511</v>
+        <v>1264</v>
       </c>
       <c r="S16" t="n">
-        <v>760</v>
+        <v>585</v>
       </c>
       <c r="T16" t="n">
-        <v>209</v>
+        <v>133</v>
       </c>
       <c r="U16" t="n">
         <v>4120</v>
@@ -1770,25 +1770,25 @@
         <v>132</v>
       </c>
       <c r="N17" t="n">
-        <v>1177</v>
+        <v>1128</v>
       </c>
       <c r="O17" t="n">
-        <v>977</v>
+        <v>930</v>
       </c>
       <c r="P17" t="n">
-        <v>910</v>
+        <v>864</v>
       </c>
       <c r="Q17" t="n">
-        <v>702</v>
+        <v>659</v>
       </c>
       <c r="R17" t="n">
-        <v>533</v>
+        <v>495</v>
       </c>
       <c r="S17" t="n">
-        <v>262</v>
+        <v>231</v>
       </c>
       <c r="T17" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="U17" t="n">
         <v>1849</v>
@@ -1849,25 +1849,25 @@
         <v>1818</v>
       </c>
       <c r="N18" t="n">
-        <v>8992</v>
+        <v>8296</v>
       </c>
       <c r="O18" t="n">
-        <v>7949</v>
+        <v>7298</v>
       </c>
       <c r="P18" t="n">
-        <v>7529</v>
+        <v>6892</v>
       </c>
       <c r="Q18" t="n">
-        <v>6139</v>
+        <v>5558</v>
       </c>
       <c r="R18" t="n">
-        <v>4867</v>
+        <v>4332</v>
       </c>
       <c r="S18" t="n">
-        <v>2516</v>
+        <v>2117</v>
       </c>
       <c r="T18" t="n">
-        <v>812</v>
+        <v>618</v>
       </c>
       <c r="U18" t="n">
         <v>13257</v>
@@ -1928,25 +1928,25 @@
         <v>340</v>
       </c>
       <c r="N19" t="n">
-        <v>2529</v>
+        <v>2381</v>
       </c>
       <c r="O19" t="n">
-        <v>2233</v>
+        <v>2087</v>
       </c>
       <c r="P19" t="n">
-        <v>2130</v>
+        <v>1987</v>
       </c>
       <c r="Q19" t="n">
-        <v>1675</v>
+        <v>1543</v>
       </c>
       <c r="R19" t="n">
-        <v>1328</v>
+        <v>1208</v>
       </c>
       <c r="S19" t="n">
-        <v>631</v>
+        <v>543</v>
       </c>
       <c r="T19" t="n">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="U19" t="n">
         <v>3533</v>
@@ -2165,19 +2165,19 @@
         <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -2244,25 +2244,25 @@
         <v>38</v>
       </c>
       <c r="N23" t="n">
-        <v>488</v>
+        <v>465</v>
       </c>
       <c r="O23" t="n">
-        <v>438</v>
+        <v>415</v>
       </c>
       <c r="P23" t="n">
-        <v>418</v>
+        <v>396</v>
       </c>
       <c r="Q23" t="n">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="R23" t="n">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="S23" t="n">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="T23" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="U23" t="n">
         <v>769</v>
@@ -2323,19 +2323,19 @@
         <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -2402,25 +2402,25 @@
         <v>9</v>
       </c>
       <c r="N25" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O25" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P25" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q25" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R25" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U25" t="n">
         <v>464</v>
@@ -2481,22 +2481,22 @@
         <v>6</v>
       </c>
       <c r="N26" t="n">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="O26" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="P26" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Q26" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="R26" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="S26" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="T26" t="n">
         <v>5</v>
@@ -3113,25 +3113,25 @@
         <v>7</v>
       </c>
       <c r="N34" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="R34" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U34" t="n">
         <v>23</v>
@@ -3192,25 +3192,25 @@
         <v>237</v>
       </c>
       <c r="N35" t="n">
-        <v>992</v>
+        <v>894</v>
       </c>
       <c r="O35" t="n">
-        <v>940</v>
+        <v>849</v>
       </c>
       <c r="P35" t="n">
-        <v>935</v>
+        <v>844</v>
       </c>
       <c r="Q35" t="n">
-        <v>682</v>
+        <v>605</v>
       </c>
       <c r="R35" t="n">
-        <v>562</v>
+        <v>498</v>
       </c>
       <c r="S35" t="n">
-        <v>243</v>
+        <v>210</v>
       </c>
       <c r="T35" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="U35" t="n">
         <v>3497</v>
@@ -3271,25 +3271,25 @@
         <v>29</v>
       </c>
       <c r="N36" t="n">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="O36" t="n">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="P36" t="n">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="Q36" t="n">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="R36" t="n">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="S36" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="T36" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="U36" t="n">
         <v>464</v>
@@ -3350,13 +3350,13 @@
         <v>3</v>
       </c>
       <c r="N37" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="O37" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P37" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Q37" t="n">
         <v>16</v>
@@ -4140,22 +4140,22 @@
         <v>3274</v>
       </c>
       <c r="N47" t="n">
-        <v>4301</v>
+        <v>4192</v>
       </c>
       <c r="O47" t="n">
-        <v>2407</v>
+        <v>2333</v>
       </c>
       <c r="P47" t="n">
-        <v>1893</v>
+        <v>1832</v>
       </c>
       <c r="Q47" t="n">
-        <v>911</v>
+        <v>867</v>
       </c>
       <c r="R47" t="n">
-        <v>419</v>
+        <v>398</v>
       </c>
       <c r="S47" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
@@ -4219,22 +4219,22 @@
         <v>53</v>
       </c>
       <c r="N48" t="n">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O48" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P48" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="Q48" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="R48" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="S48" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T48" t="n">
         <v>30</v>
@@ -4298,19 +4298,19 @@
         <v>532</v>
       </c>
       <c r="N49" t="n">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="O49" t="n">
-        <v>281</v>
+        <v>243</v>
       </c>
       <c r="P49" t="n">
-        <v>249</v>
+        <v>213</v>
       </c>
       <c r="Q49" t="n">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="R49" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -4377,25 +4377,25 @@
         <v>112</v>
       </c>
       <c r="N50" t="n">
-        <v>216</v>
+        <v>155</v>
       </c>
       <c r="O50" t="n">
-        <v>199</v>
+        <v>138</v>
       </c>
       <c r="P50" t="n">
-        <v>196</v>
+        <v>135</v>
       </c>
       <c r="Q50" t="n">
-        <v>178</v>
+        <v>118</v>
       </c>
       <c r="R50" t="n">
-        <v>150</v>
+        <v>92</v>
       </c>
       <c r="S50" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="T50" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="U50" t="n">
         <v>411</v>
@@ -4456,25 +4456,25 @@
         <v>15</v>
       </c>
       <c r="N51" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="O51" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="P51" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="Q51" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="R51" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="S51" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="T51" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="U51" t="n">
         <v>178</v>
@@ -4614,19 +4614,19 @@
         <v>141</v>
       </c>
       <c r="N53" t="n">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="O53" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="P53" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="Q53" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="R53" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -4693,22 +4693,22 @@
         <v>3177</v>
       </c>
       <c r="N54" t="n">
-        <v>5833</v>
+        <v>5693</v>
       </c>
       <c r="O54" t="n">
-        <v>2654</v>
+        <v>2573</v>
       </c>
       <c r="P54" t="n">
-        <v>1951</v>
+        <v>1889</v>
       </c>
       <c r="Q54" t="n">
-        <v>745</v>
+        <v>716</v>
       </c>
       <c r="R54" t="n">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="S54" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="T54" t="n">
         <v>1</v>
@@ -4851,19 +4851,19 @@
         <v>1218</v>
       </c>
       <c r="N56" t="n">
-        <v>2900</v>
+        <v>2832</v>
       </c>
       <c r="O56" t="n">
-        <v>971</v>
+        <v>933</v>
       </c>
       <c r="P56" t="n">
-        <v>619</v>
+        <v>591</v>
       </c>
       <c r="Q56" t="n">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="R56" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="S56" t="n">
         <v>8</v>
@@ -5404,22 +5404,22 @@
         <v>175</v>
       </c>
       <c r="N63" t="n">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="O63" t="n">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="P63" t="n">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="Q63" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="R63" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S63" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
@@ -5483,25 +5483,25 @@
         <v>1</v>
       </c>
       <c r="N64" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O64" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P64" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q64" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R64" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T64" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U64" t="n">
         <v>487</v>
@@ -5799,25 +5799,25 @@
         <v>1</v>
       </c>
       <c r="N68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U68" t="n">
         <v>60</v>
@@ -5957,22 +5957,22 @@
         <v>122</v>
       </c>
       <c r="N70" t="n">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="O70" t="n">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="P70" t="n">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="Q70" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="R70" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="S70" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="T70" t="n">
         <v>11</v>
@@ -6036,25 +6036,25 @@
         <v>6</v>
       </c>
       <c r="N71" t="n">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="O71" t="n">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="P71" t="n">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="Q71" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="R71" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="S71" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T71" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U71" t="n">
         <v>1018</v>
@@ -6115,25 +6115,25 @@
         <v>27</v>
       </c>
       <c r="N72" t="n">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="O72" t="n">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="P72" t="n">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="Q72" t="n">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="R72" t="n">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="S72" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T72" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U72" t="n">
         <v>888</v>
@@ -6194,22 +6194,22 @@
         <v>7</v>
       </c>
       <c r="N73" t="n">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="O73" t="n">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="P73" t="n">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="Q73" t="n">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="R73" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="S73" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="T73" t="n">
         <v>14</v>
@@ -6510,25 +6510,25 @@
         <v>28</v>
       </c>
       <c r="N77" t="n">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="O77" t="n">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="P77" t="n">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="Q77" t="n">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="R77" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="S77" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T77" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="U77" t="n">
         <v>1860</v>
@@ -7142,22 +7142,22 @@
         <v>94</v>
       </c>
       <c r="N85" t="n">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="O85" t="n">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="P85" t="n">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="Q85" t="n">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="R85" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="S85" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T85" t="n">
         <v>33</v>
@@ -7616,19 +7616,19 @@
         <v>292</v>
       </c>
       <c r="N91" t="n">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="O91" t="n">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="P91" t="n">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="Q91" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="R91" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S91" t="n">
         <v>34</v>
@@ -7695,25 +7695,25 @@
         <v>160</v>
       </c>
       <c r="N92" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O92" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P92" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q92" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U92" t="n">
         <v>12573</v>
@@ -7774,7 +7774,7 @@
         <v>26</v>
       </c>
       <c r="N93" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O93" t="n">
         <v>25</v>
@@ -8090,22 +8090,22 @@
         <v>18</v>
       </c>
       <c r="N97" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O97" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P97" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q97" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R97" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S97" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="T97" t="n">
         <v>4</v>
@@ -8327,19 +8327,19 @@
         <v>29</v>
       </c>
       <c r="N100" t="n">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="O100" t="n">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="P100" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q100" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="R100" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="S100" t="n">
         <v>7</v>
@@ -8406,25 +8406,25 @@
         <v>535</v>
       </c>
       <c r="N101" t="n">
-        <v>5850</v>
+        <v>5776</v>
       </c>
       <c r="O101" t="n">
-        <v>3562</v>
+        <v>3505</v>
       </c>
       <c r="P101" t="n">
-        <v>2874</v>
+        <v>2818</v>
       </c>
       <c r="Q101" t="n">
-        <v>1445</v>
+        <v>1405</v>
       </c>
       <c r="R101" t="n">
-        <v>751</v>
+        <v>726</v>
       </c>
       <c r="S101" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="T101" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U101" t="n">
         <v>29325</v>
@@ -8485,19 +8485,19 @@
         <v>73</v>
       </c>
       <c r="N102" t="n">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="O102" t="n">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="P102" t="n">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="Q102" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="R102" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S102" t="n">
         <v>16</v>
@@ -8643,22 +8643,22 @@
         <v>4</v>
       </c>
       <c r="N104" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O104" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P104" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q104" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R104" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S104" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T104" t="n">
         <v>1</v>
@@ -8722,19 +8722,19 @@
         <v>122</v>
       </c>
       <c r="N105" t="n">
-        <v>2531</v>
+        <v>2525</v>
       </c>
       <c r="O105" t="n">
-        <v>1301</v>
+        <v>1296</v>
       </c>
       <c r="P105" t="n">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Q105" t="n">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="R105" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="S105" t="n">
         <v>28</v>
@@ -9196,19 +9196,19 @@
         <v>378</v>
       </c>
       <c r="N111" t="n">
-        <v>4048</v>
+        <v>4006</v>
       </c>
       <c r="O111" t="n">
-        <v>2242</v>
+        <v>2211</v>
       </c>
       <c r="P111" t="n">
-        <v>1736</v>
+        <v>1712</v>
       </c>
       <c r="Q111" t="n">
-        <v>767</v>
+        <v>758</v>
       </c>
       <c r="R111" t="n">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="S111" t="n">
         <v>57</v>
@@ -9275,22 +9275,22 @@
         <v>53</v>
       </c>
       <c r="N112" t="n">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="O112" t="n">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="P112" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="Q112" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="R112" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="S112" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T112" t="n">
         <v>1</v>
@@ -9828,25 +9828,25 @@
         <v>14</v>
       </c>
       <c r="N119" t="n">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="O119" t="n">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="P119" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="Q119" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="R119" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="S119" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="T119" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U119" t="n">
         <v>675</v>
@@ -9907,25 +9907,25 @@
         <v>51</v>
       </c>
       <c r="N120" t="n">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="O120" t="n">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="P120" t="n">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="Q120" t="n">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="R120" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="S120" t="n">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="T120" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="U120" t="n">
         <v>1949</v>
@@ -10618,25 +10618,25 @@
         <v>171</v>
       </c>
       <c r="N129" t="n">
-        <v>3339</v>
+        <v>3278</v>
       </c>
       <c r="O129" t="n">
-        <v>2036</v>
+        <v>1982</v>
       </c>
       <c r="P129" t="n">
-        <v>2036</v>
+        <v>1982</v>
       </c>
       <c r="Q129" t="n">
-        <v>1512</v>
+        <v>1465</v>
       </c>
       <c r="R129" t="n">
-        <v>1175</v>
+        <v>1130</v>
       </c>
       <c r="S129" t="n">
-        <v>700</v>
+        <v>661</v>
       </c>
       <c r="T129" t="n">
-        <v>319</v>
+        <v>297</v>
       </c>
       <c r="U129" t="n">
         <v>13822</v>
@@ -10697,25 +10697,25 @@
         <v>15</v>
       </c>
       <c r="N130" t="n">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="O130" t="n">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="P130" t="n">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="Q130" t="n">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="R130" t="n">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="S130" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="T130" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="U130" t="n">
         <v>1360</v>
@@ -11329,25 +11329,25 @@
         <v>60</v>
       </c>
       <c r="N138" t="n">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="O138" t="n">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="P138" t="n">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="Q138" t="n">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="R138" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="S138" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="T138" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U138" t="n">
         <v>1295</v>
@@ -11645,7 +11645,7 @@
         <v>22</v>
       </c>
       <c r="N142" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O142" t="n">
         <v>19</v>
@@ -11803,16 +11803,16 @@
         <v>19</v>
       </c>
       <c r="N144" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="O144" t="n">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="P144" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q144" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="R144" t="n">
         <v>117</v>
@@ -11961,25 +11961,25 @@
         <v>178</v>
       </c>
       <c r="N146" t="n">
-        <v>3417</v>
+        <v>3384</v>
       </c>
       <c r="O146" t="n">
-        <v>2786</v>
+        <v>2753</v>
       </c>
       <c r="P146" t="n">
-        <v>2546</v>
+        <v>2513</v>
       </c>
       <c r="Q146" t="n">
-        <v>1834</v>
+        <v>1802</v>
       </c>
       <c r="R146" t="n">
-        <v>1341</v>
+        <v>1313</v>
       </c>
       <c r="S146" t="n">
-        <v>695</v>
+        <v>667</v>
       </c>
       <c r="T146" t="n">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="U146" t="n">
         <v>6650</v>
@@ -12040,25 +12040,25 @@
         <v>98</v>
       </c>
       <c r="N147" t="n">
-        <v>1462</v>
+        <v>1444</v>
       </c>
       <c r="O147" t="n">
-        <v>1211</v>
+        <v>1194</v>
       </c>
       <c r="P147" t="n">
-        <v>1118</v>
+        <v>1101</v>
       </c>
       <c r="Q147" t="n">
-        <v>832</v>
+        <v>817</v>
       </c>
       <c r="R147" t="n">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="S147" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="T147" t="n">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="U147" t="n">
         <v>3051</v>
@@ -12435,19 +12435,19 @@
         <v>655</v>
       </c>
       <c r="N152" t="n">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="O152" t="n">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="P152" t="n">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="Q152" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="R152" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -12830,25 +12830,25 @@
         <v>10020</v>
       </c>
       <c r="N157" t="n">
-        <v>48231</v>
+        <v>47662</v>
       </c>
       <c r="O157" t="n">
-        <v>28097</v>
+        <v>27648</v>
       </c>
       <c r="P157" t="n">
-        <v>22320</v>
+        <v>21921</v>
       </c>
       <c r="Q157" t="n">
-        <v>11503</v>
+        <v>11217</v>
       </c>
       <c r="R157" t="n">
-        <v>6671</v>
+        <v>6460</v>
       </c>
       <c r="S157" t="n">
-        <v>2235</v>
+        <v>2142</v>
       </c>
       <c r="T157" t="n">
-        <v>488</v>
+        <v>461</v>
       </c>
       <c r="U157" t="n">
         <v>220151</v>
@@ -12909,22 +12909,22 @@
         <v>481</v>
       </c>
       <c r="N158" t="n">
-        <v>1267</v>
+        <v>1239</v>
       </c>
       <c r="O158" t="n">
-        <v>757</v>
+        <v>738</v>
       </c>
       <c r="P158" t="n">
-        <v>615</v>
+        <v>597</v>
       </c>
       <c r="Q158" t="n">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="R158" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="S158" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T158" t="n">
         <v>5</v>
@@ -13383,16 +13383,16 @@
         <v>54</v>
       </c>
       <c r="N164" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="O164" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="P164" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="Q164" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="R164" t="n">
         <v>10</v>
@@ -14331,25 +14331,25 @@
         <v>8</v>
       </c>
       <c r="N176" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="O176" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="P176" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Q176" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="R176" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S176" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T176" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U176" t="n">
         <v>36</v>
@@ -14797,25 +14797,25 @@
         <v>47</v>
       </c>
       <c r="N182" t="n">
-        <v>188</v>
+        <v>158</v>
       </c>
       <c r="O182" t="n">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="P182" t="n">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="Q182" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="R182" t="n">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="S182" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="T182" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U182" t="n">
         <v>360</v>
@@ -15323,25 +15323,25 @@
         <v>13</v>
       </c>
       <c r="O2" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="P2" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="Q2" t="n">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="R2" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="S2" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T2" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="U2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V2" t="n">
         <v>673</v>
@@ -16247,25 +16247,25 @@
         <v>51</v>
       </c>
       <c r="O13" t="n">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="P13" t="n">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="Q13" t="n">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="R13" t="n">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="S13" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="T13" t="n">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="U13" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="V13" t="n">
         <v>1949</v>
@@ -16667,25 +16667,25 @@
         <v>171</v>
       </c>
       <c r="O18" t="n">
-        <v>3339</v>
+        <v>3278</v>
       </c>
       <c r="P18" t="n">
-        <v>2036</v>
+        <v>1982</v>
       </c>
       <c r="Q18" t="n">
-        <v>2036</v>
+        <v>1982</v>
       </c>
       <c r="R18" t="n">
-        <v>1512</v>
+        <v>1465</v>
       </c>
       <c r="S18" t="n">
-        <v>1175</v>
+        <v>1130</v>
       </c>
       <c r="T18" t="n">
-        <v>700</v>
+        <v>661</v>
       </c>
       <c r="U18" t="n">
-        <v>319</v>
+        <v>297</v>
       </c>
       <c r="V18" t="n">
         <v>13822</v>
@@ -16751,25 +16751,25 @@
         <v>15</v>
       </c>
       <c r="O19" t="n">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="P19" t="n">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="Q19" t="n">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="R19" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="S19" t="n">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="T19" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="U19" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="V19" t="n">
         <v>1305</v>
@@ -17045,22 +17045,22 @@
         <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q2" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U2" t="n">
         <v>6</v>
@@ -17297,19 +17297,19 @@
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T5" t="n">
         <v>3</v>
@@ -17381,22 +17381,22 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U6" t="n">
         <v>2</v>
@@ -17465,25 +17465,25 @@
         <v>14</v>
       </c>
       <c r="O7" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="P7" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="Q7" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="R7" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
         <v>60</v>
@@ -17549,25 +17549,25 @@
         <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V8" t="n">
         <v>59</v>
@@ -17633,25 +17633,25 @@
         <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="S9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V9" t="n">
         <v>55</v>
@@ -17801,25 +17801,25 @@
         <v>738</v>
       </c>
       <c r="O11" t="n">
-        <v>2790</v>
+        <v>2468</v>
       </c>
       <c r="P11" t="n">
-        <v>2466</v>
+        <v>2156</v>
       </c>
       <c r="Q11" t="n">
-        <v>2331</v>
+        <v>2027</v>
       </c>
       <c r="R11" t="n">
-        <v>1878</v>
+        <v>1610</v>
       </c>
       <c r="S11" t="n">
-        <v>1502</v>
+        <v>1255</v>
       </c>
       <c r="T11" t="n">
-        <v>760</v>
+        <v>585</v>
       </c>
       <c r="U11" t="n">
-        <v>209</v>
+        <v>133</v>
       </c>
       <c r="V11" t="n">
         <v>4100</v>
@@ -17885,25 +17885,25 @@
         <v>61</v>
       </c>
       <c r="O12" t="n">
-        <v>366</v>
+        <v>344</v>
       </c>
       <c r="P12" t="n">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="Q12" t="n">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="R12" t="n">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="S12" t="n">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="T12" t="n">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="U12" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="V12" t="n">
         <v>411</v>
@@ -17969,25 +17969,25 @@
         <v>1818</v>
       </c>
       <c r="O13" t="n">
-        <v>8992</v>
+        <v>8296</v>
       </c>
       <c r="P13" t="n">
-        <v>7949</v>
+        <v>7298</v>
       </c>
       <c r="Q13" t="n">
-        <v>7529</v>
+        <v>6892</v>
       </c>
       <c r="R13" t="n">
-        <v>6139</v>
+        <v>5558</v>
       </c>
       <c r="S13" t="n">
-        <v>4867</v>
+        <v>4332</v>
       </c>
       <c r="T13" t="n">
-        <v>2516</v>
+        <v>2117</v>
       </c>
       <c r="U13" t="n">
-        <v>812</v>
+        <v>618</v>
       </c>
       <c r="V13" t="n">
         <v>13257</v>
@@ -18137,19 +18137,19 @@
         <v>3</v>
       </c>
       <c r="O15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
@@ -18221,25 +18221,25 @@
         <v>8</v>
       </c>
       <c r="O16" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P16" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="Q16" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="R16" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S16" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="T16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V16" t="n">
         <v>357</v>
@@ -18641,25 +18641,25 @@
         <v>135</v>
       </c>
       <c r="O21" t="n">
-        <v>309</v>
+        <v>244</v>
       </c>
       <c r="P21" t="n">
-        <v>281</v>
+        <v>217</v>
       </c>
       <c r="Q21" t="n">
-        <v>262</v>
+        <v>199</v>
       </c>
       <c r="R21" t="n">
-        <v>221</v>
+        <v>161</v>
       </c>
       <c r="S21" t="n">
-        <v>188</v>
+        <v>131</v>
       </c>
       <c r="T21" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="U21" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="V21" t="n">
         <v>377</v>
@@ -18725,25 +18725,25 @@
         <v>12</v>
       </c>
       <c r="O22" t="n">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="P22" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="Q22" t="n">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="R22" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="S22" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="T22" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="U22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V22" t="n">
         <v>218</v>
@@ -18893,25 +18893,25 @@
         <v>26</v>
       </c>
       <c r="O24" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="P24" t="n">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="Q24" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="R24" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="S24" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="T24" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="U24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V24" t="n">
         <v>167</v>
@@ -18977,25 +18977,25 @@
         <v>45</v>
       </c>
       <c r="O25" t="n">
-        <v>515</v>
+        <v>490</v>
       </c>
       <c r="P25" t="n">
-        <v>463</v>
+        <v>438</v>
       </c>
       <c r="Q25" t="n">
-        <v>441</v>
+        <v>418</v>
       </c>
       <c r="R25" t="n">
-        <v>369</v>
+        <v>347</v>
       </c>
       <c r="S25" t="n">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="T25" t="n">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="U25" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="V25" t="n">
         <v>677</v>
@@ -19061,25 +19061,25 @@
         <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P26" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q26" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R26" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V26" t="n">
         <v>234</v>
@@ -19229,25 +19229,25 @@
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V28" t="n">
         <v>24</v>
@@ -19397,19 +19397,19 @@
         <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P30" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Q30" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="R30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T30" t="n">
         <v>7</v>
@@ -19565,22 +19565,22 @@
         <v>10</v>
       </c>
       <c r="O32" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P32" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q32" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="R32" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="S32" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="T32" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U32" t="n">
         <v>24</v>
@@ -19649,25 +19649,25 @@
         <v>14</v>
       </c>
       <c r="O33" t="n">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="P33" t="n">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="Q33" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="R33" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="S33" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="T33" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="U33" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="V33" t="n">
         <v>114</v>
@@ -19817,25 +19817,25 @@
         <v>16</v>
       </c>
       <c r="O35" t="n">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="P35" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="Q35" t="n">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="R35" t="n">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="S35" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="T35" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="U35" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V35" t="n">
         <v>357</v>
@@ -19901,25 +19901,25 @@
         <v>117</v>
       </c>
       <c r="O36" t="n">
-        <v>942</v>
+        <v>897</v>
       </c>
       <c r="P36" t="n">
-        <v>850</v>
+        <v>806</v>
       </c>
       <c r="Q36" t="n">
-        <v>805</v>
+        <v>761</v>
       </c>
       <c r="R36" t="n">
-        <v>658</v>
+        <v>619</v>
       </c>
       <c r="S36" t="n">
-        <v>528</v>
+        <v>493</v>
       </c>
       <c r="T36" t="n">
-        <v>276</v>
+        <v>249</v>
       </c>
       <c r="U36" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="V36" t="n">
         <v>1362</v>
@@ -20069,22 +20069,22 @@
         <v>24</v>
       </c>
       <c r="O38" t="n">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="P38" t="n">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q38" t="n">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="R38" t="n">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="S38" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="T38" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="U38" t="n">
         <v>2</v>
@@ -20153,25 +20153,25 @@
         <v>16</v>
       </c>
       <c r="O39" t="n">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="P39" t="n">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="Q39" t="n">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="R39" t="n">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="S39" t="n">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="T39" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="U39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V39" t="n">
         <v>668</v>
@@ -20489,19 +20489,19 @@
         <v>5</v>
       </c>
       <c r="O43" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T43" t="n">
         <v>4</v>
@@ -20573,25 +20573,25 @@
         <v>38</v>
       </c>
       <c r="O44" t="n">
-        <v>488</v>
+        <v>465</v>
       </c>
       <c r="P44" t="n">
-        <v>438</v>
+        <v>415</v>
       </c>
       <c r="Q44" t="n">
-        <v>418</v>
+        <v>396</v>
       </c>
       <c r="R44" t="n">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="S44" t="n">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="T44" t="n">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="U44" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="V44" t="n">
         <v>768</v>
@@ -20657,22 +20657,22 @@
         <v>6</v>
       </c>
       <c r="O45" t="n">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="P45" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="Q45" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="R45" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="S45" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="T45" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="U45" t="n">
         <v>5</v>
@@ -20909,22 +20909,22 @@
         <v>28</v>
       </c>
       <c r="O48" t="n">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="P48" t="n">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Q48" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="R48" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S48" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="T48" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="U48" t="n">
         <v>3</v>
@@ -21539,22 +21539,22 @@
         <v>49</v>
       </c>
       <c r="O2" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="P2" t="n">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="Q2" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="R2" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="S2" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="T2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U2" t="n">
         <v>23</v>
@@ -21623,25 +21623,25 @@
         <v>112</v>
       </c>
       <c r="O3" t="n">
-        <v>216</v>
+        <v>155</v>
       </c>
       <c r="P3" t="n">
-        <v>199</v>
+        <v>138</v>
       </c>
       <c r="Q3" t="n">
-        <v>196</v>
+        <v>135</v>
       </c>
       <c r="R3" t="n">
-        <v>178</v>
+        <v>118</v>
       </c>
       <c r="S3" t="n">
-        <v>150</v>
+        <v>92</v>
       </c>
       <c r="T3" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="U3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="V3" t="n">
         <v>411</v>
@@ -21791,22 +21791,22 @@
         <v>3274</v>
       </c>
       <c r="O5" t="n">
-        <v>4301</v>
+        <v>4192</v>
       </c>
       <c r="P5" t="n">
-        <v>2407</v>
+        <v>2333</v>
       </c>
       <c r="Q5" t="n">
-        <v>1893</v>
+        <v>1832</v>
       </c>
       <c r="R5" t="n">
-        <v>911</v>
+        <v>867</v>
       </c>
       <c r="S5" t="n">
-        <v>419</v>
+        <v>398</v>
       </c>
       <c r="T5" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="U5" t="n">
         <v>1</v>
@@ -21875,19 +21875,19 @@
         <v>532</v>
       </c>
       <c r="O6" t="n">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="P6" t="n">
-        <v>281</v>
+        <v>243</v>
       </c>
       <c r="Q6" t="n">
-        <v>249</v>
+        <v>213</v>
       </c>
       <c r="R6" t="n">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="S6" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="T6" t="n">
         <v>10</v>
@@ -22043,19 +22043,19 @@
         <v>141</v>
       </c>
       <c r="O8" t="n">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="P8" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="Q8" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="R8" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -22127,22 +22127,22 @@
         <v>3177</v>
       </c>
       <c r="O9" t="n">
-        <v>5833</v>
+        <v>5693</v>
       </c>
       <c r="P9" t="n">
-        <v>2654</v>
+        <v>2573</v>
       </c>
       <c r="Q9" t="n">
-        <v>1951</v>
+        <v>1889</v>
       </c>
       <c r="R9" t="n">
-        <v>745</v>
+        <v>716</v>
       </c>
       <c r="S9" t="n">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="T9" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="U9" t="n">
         <v>1</v>
@@ -22295,19 +22295,19 @@
         <v>1218</v>
       </c>
       <c r="O11" t="n">
-        <v>2900</v>
+        <v>2832</v>
       </c>
       <c r="P11" t="n">
-        <v>971</v>
+        <v>933</v>
       </c>
       <c r="Q11" t="n">
-        <v>619</v>
+        <v>591</v>
       </c>
       <c r="R11" t="n">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="S11" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="T11" t="n">
         <v>8</v>
@@ -22463,25 +22463,25 @@
         <v>15</v>
       </c>
       <c r="O13" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="P13" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="Q13" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="R13" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="S13" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="T13" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="U13" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="V13" t="n">
         <v>178</v>
@@ -23093,25 +23093,25 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P7" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q7" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R7" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S7" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
         <v>450</v>
@@ -23849,19 +23849,19 @@
         <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P16" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T16" t="n">
         <v>6</v>
@@ -24857,25 +24857,25 @@
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>72</v>
@@ -25529,22 +25529,22 @@
         <v>175</v>
       </c>
       <c r="O36" t="n">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="P36" t="n">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="Q36" t="n">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="R36" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="S36" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="T36" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="U36" t="n">
         <v>1</v>
@@ -25781,25 +25781,25 @@
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
         <v>60</v>
@@ -25949,22 +25949,22 @@
         <v>122</v>
       </c>
       <c r="O41" t="n">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="P41" t="n">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="Q41" t="n">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="R41" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="S41" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="T41" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U41" t="n">
         <v>11</v>
@@ -26117,25 +26117,25 @@
         <v>27</v>
       </c>
       <c r="O43" t="n">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="P43" t="n">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="Q43" t="n">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="R43" t="n">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="S43" t="n">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="T43" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="U43" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V43" t="n">
         <v>888</v>
@@ -26201,22 +26201,22 @@
         <v>7</v>
       </c>
       <c r="O44" t="n">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="P44" t="n">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="Q44" t="n">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="R44" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="S44" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="T44" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="U44" t="n">
         <v>13</v>
@@ -27167,22 +27167,22 @@
         <v>11</v>
       </c>
       <c r="O4" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P4" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="S4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U4" t="n">
         <v>2</v>
@@ -27335,22 +27335,22 @@
         <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="P6" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Q6" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="R6" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="U6" t="n">
         <v>14</v>
@@ -27503,19 +27503,19 @@
         <v>292</v>
       </c>
       <c r="O8" t="n">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="P8" t="n">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="Q8" t="n">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="R8" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="S8" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T8" t="n">
         <v>34</v>
@@ -27923,22 +27923,22 @@
         <v>18</v>
       </c>
       <c r="O13" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P13" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q13" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S13" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="T13" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U13" t="n">
         <v>4</v>
@@ -28595,25 +28595,25 @@
         <v>160</v>
       </c>
       <c r="O21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
         <v>12573</v>
@@ -28679,7 +28679,7 @@
         <v>26</v>
       </c>
       <c r="O22" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P22" t="n">
         <v>25</v>
@@ -28931,13 +28931,13 @@
         <v>62</v>
       </c>
       <c r="O25" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P25" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R25" t="n">
         <v>25</v>
@@ -29225,22 +29225,22 @@
         <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P2" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q2" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R2" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="S2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
@@ -29309,19 +29309,19 @@
         <v>29</v>
       </c>
       <c r="O3" t="n">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="P3" t="n">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="Q3" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="R3" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="S3" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="T3" t="n">
         <v>7</v>
@@ -29477,25 +29477,25 @@
         <v>535</v>
       </c>
       <c r="O5" t="n">
-        <v>5850</v>
+        <v>5776</v>
       </c>
       <c r="P5" t="n">
-        <v>3562</v>
+        <v>3505</v>
       </c>
       <c r="Q5" t="n">
-        <v>2874</v>
+        <v>2818</v>
       </c>
       <c r="R5" t="n">
-        <v>1445</v>
+        <v>1405</v>
       </c>
       <c r="S5" t="n">
-        <v>751</v>
+        <v>726</v>
       </c>
       <c r="T5" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="U5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V5" t="n">
         <v>29325</v>
@@ -29561,19 +29561,19 @@
         <v>73</v>
       </c>
       <c r="O6" t="n">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="P6" t="n">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="Q6" t="n">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="R6" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="S6" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T6" t="n">
         <v>16</v>
@@ -29729,19 +29729,19 @@
         <v>122</v>
       </c>
       <c r="O8" t="n">
-        <v>2531</v>
+        <v>2525</v>
       </c>
       <c r="P8" t="n">
-        <v>1301</v>
+        <v>1296</v>
       </c>
       <c r="Q8" t="n">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="R8" t="n">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="S8" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T8" t="n">
         <v>28</v>
@@ -30149,19 +30149,19 @@
         <v>378</v>
       </c>
       <c r="O13" t="n">
-        <v>4048</v>
+        <v>4006</v>
       </c>
       <c r="P13" t="n">
-        <v>2242</v>
+        <v>2211</v>
       </c>
       <c r="Q13" t="n">
-        <v>1736</v>
+        <v>1712</v>
       </c>
       <c r="R13" t="n">
-        <v>767</v>
+        <v>758</v>
       </c>
       <c r="S13" t="n">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="T13" t="n">
         <v>57</v>
@@ -30233,22 +30233,22 @@
         <v>53</v>
       </c>
       <c r="O14" t="n">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="P14" t="n">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="Q14" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="R14" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="S14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="T14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U14" t="n">
         <v>1</v>
@@ -31955,25 +31955,25 @@
         <v>56</v>
       </c>
       <c r="O18" t="n">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="P18" t="n">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="Q18" t="n">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="R18" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="S18" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="T18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="U18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V18" t="n">
         <v>920</v>
@@ -32291,7 +32291,7 @@
         <v>22</v>
       </c>
       <c r="O22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P22" t="n">
         <v>19</v>
@@ -32459,16 +32459,16 @@
         <v>19</v>
       </c>
       <c r="O24" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="P24" t="n">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Q24" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="R24" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="S24" t="n">
         <v>117</v>
@@ -32627,25 +32627,25 @@
         <v>178</v>
       </c>
       <c r="O26" t="n">
-        <v>3417</v>
+        <v>3384</v>
       </c>
       <c r="P26" t="n">
-        <v>2786</v>
+        <v>2753</v>
       </c>
       <c r="Q26" t="n">
-        <v>2546</v>
+        <v>2513</v>
       </c>
       <c r="R26" t="n">
-        <v>1834</v>
+        <v>1802</v>
       </c>
       <c r="S26" t="n">
-        <v>1341</v>
+        <v>1313</v>
       </c>
       <c r="T26" t="n">
-        <v>695</v>
+        <v>667</v>
       </c>
       <c r="U26" t="n">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="V26" t="n">
         <v>6650</v>
@@ -32711,25 +32711,25 @@
         <v>98</v>
       </c>
       <c r="O27" t="n">
-        <v>1462</v>
+        <v>1444</v>
       </c>
       <c r="P27" t="n">
-        <v>1211</v>
+        <v>1194</v>
       </c>
       <c r="Q27" t="n">
-        <v>1118</v>
+        <v>1101</v>
       </c>
       <c r="R27" t="n">
-        <v>832</v>
+        <v>817</v>
       </c>
       <c r="S27" t="n">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="T27" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="U27" t="n">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="V27" t="n">
         <v>3051</v>
@@ -32963,19 +32963,19 @@
         <v>655</v>
       </c>
       <c r="O30" t="n">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="P30" t="n">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="Q30" t="n">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="R30" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="S30" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="T30" t="n">
         <v>10</v>
@@ -33215,25 +33215,25 @@
         <v>10020</v>
       </c>
       <c r="O33" t="n">
-        <v>48231</v>
+        <v>47662</v>
       </c>
       <c r="P33" t="n">
-        <v>28097</v>
+        <v>27648</v>
       </c>
       <c r="Q33" t="n">
-        <v>22320</v>
+        <v>21921</v>
       </c>
       <c r="R33" t="n">
-        <v>11503</v>
+        <v>11217</v>
       </c>
       <c r="S33" t="n">
-        <v>6671</v>
+        <v>6460</v>
       </c>
       <c r="T33" t="n">
-        <v>2235</v>
+        <v>2142</v>
       </c>
       <c r="U33" t="n">
-        <v>488</v>
+        <v>461</v>
       </c>
       <c r="V33" t="n">
         <v>220151</v>
@@ -33299,22 +33299,22 @@
         <v>481</v>
       </c>
       <c r="O34" t="n">
-        <v>1266</v>
+        <v>1238</v>
       </c>
       <c r="P34" t="n">
-        <v>756</v>
+        <v>737</v>
       </c>
       <c r="Q34" t="n">
-        <v>614</v>
+        <v>596</v>
       </c>
       <c r="R34" t="n">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="S34" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="T34" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="U34" t="n">
         <v>5</v>
